--- a/imageCreationExcel/Bright/Master/MASTER_7.xlsx
+++ b/imageCreationExcel/Bright/Master/MASTER_7.xlsx
@@ -606,15 +606,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\4_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>M_7_2_4_match_4_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_7_2_4_match_4_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -660,15 +666,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\4_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>M_7_3_D_filler_4_day_sun_empty_MODEL.jpg</t>
+          <t>M_7_3_D_filler_4_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -768,15 +792,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\6_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>M_7_5_6_match_6_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_7_5_6_match_6_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -822,15 +852,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\4_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>M_7_6_A_filler_4_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_7_6_A_filler_4_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -984,15 +1020,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\5_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>M_7_9_C_filler_5_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_7_9_C_filler_5_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -1146,15 +1188,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\8_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>M_7_12_U_filler_8_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_7_12_U_filler_8_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -1200,15 +1248,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\0_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>M_7_13_D_filler_0_day_rain_busy_MODEL.jpg</t>
+          <t>M_7_13_D_filler_0_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -1254,15 +1320,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\4_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>M_7_14_7_unmatch_4_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_7_14_7_unmatch_4_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -1308,15 +1380,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\1_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>M_7_15_C_filler_1_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_7_15_C_filler_1_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -1362,15 +1440,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\1_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>M_7_16_B_filler_1_day_rain_empty_MODEL.jpg</t>
+          <t>M_7_16_B_filler_1_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -1416,15 +1512,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\9_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>M_7_17_T_filler_9_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_7_17_T_filler_9_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -1524,15 +1626,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\6_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>M_7_19_G_filler_6_day_sun_empty_MODEL.jpg</t>
+          <t>M_7_19_G_filler_6_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -1632,15 +1752,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\9_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>M_7_21_G_filler_9_day_rain_empty_MODEL.jpg</t>
+          <t>M_7_21_G_filler_9_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -1686,15 +1824,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\5_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>M_7_22_5_match_5_day_rain_busy_MODEL.jpg</t>
+          <t>M_7_22_5_match_5_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -1794,15 +1950,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\0_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>M_7_24_G_filler_0_day_rain_busy_MODEL.jpg</t>
+          <t>M_7_24_G_filler_0_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -1848,15 +2022,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\9_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>M_7_25_Q_filler_9_day_sun_busy_MODEL.jpg</t>
+          <t>M_7_25_Q_filler_9_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -1902,15 +2094,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\9_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>M_7_26_5_unmatch_9_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_7_26_5_unmatch_9_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -2010,15 +2208,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\2_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>M_7_28_R_filler_2_day_sun_empty_MODEL.jpg</t>
+          <t>M_7_28_R_filler_2_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -2118,15 +2334,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\3_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>M_7_30_J_filler_3_day_sun_busy_MODEL.jpg</t>
+          <t>M_7_30_J_filler_3_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -2172,15 +2406,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\7_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>M_7_31_D_filler_7_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_7_31_D_filler_7_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -2226,15 +2466,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\2_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>M_7_32_5_unmatch_2_day_sun_busy_MODEL.jpg</t>
+          <t>M_7_32_5_unmatch_2_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -2280,15 +2538,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\8_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>M_7_33_A_filler_8_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_7_33_A_filler_8_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -2334,15 +2598,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\6_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>M_7_34_6_match_6_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_7_34_6_match_6_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -2388,15 +2658,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\2_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>M_7_35_T_filler_2_day_rain_empty_MODEL.jpg</t>
+          <t>M_7_35_T_filler_2_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -2442,15 +2730,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\6_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>M_7_36_6_match_6_day_sun_empty_MODEL.jpg</t>
+          <t>M_7_36_6_match_6_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -2496,15 +2802,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\7_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>M_7_37_L_filler_7_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_7_37_L_filler_7_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -2550,15 +2862,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\2_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>M_7_38_Q_filler_2_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_7_38_Q_filler_2_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -2712,15 +3030,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\1_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>M_7_41_1_match_1_day_sun_empty_MODEL.jpg</t>
+          <t>M_7_41_1_match_1_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -2874,15 +3210,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\8_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>M_7_44_P_filler_8_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_7_44_P_filler_8_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -2928,15 +3270,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\4_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>M_7_45_8_unmatch_4_day_sun_busy_MODEL.jpg</t>
+          <t>M_7_45_8_unmatch_4_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -2982,15 +3342,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\8_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>M_7_46_L_filler_8_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_7_46_L_filler_8_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -3036,15 +3402,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\7_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>M_7_47_5_unmatch_7_day_sun_empty_MODEL.jpg</t>
+          <t>M_7_47_5_unmatch_7_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
